--- a/pcb/robot/usb-pd-module/USB_PD_Module_BOM.xlsx
+++ b/pcb/robot/usb-pd-module/USB_PD_Module_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JHORDAN\FREELANCE\PROYECTOS\KICAD_USB_PD_MODULAR\Github\smartphone-robot-cad\pcb\robot\usb-pd-module\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0526A142-8673-4CFE-B2F1-9A8F85F987FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061915B7-0919-4C28-9B35-08341C0054FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="79">
   <si>
     <t>Footprint</t>
   </si>
@@ -72,15 +72,6 @@
     <t>GRM188R61E475KE11D</t>
   </si>
   <si>
-    <t>MountingHole</t>
-  </si>
-  <si>
-    <t>H1,H2</t>
-  </si>
-  <si>
-    <t>robot:MountingHole_2.2mm_M2_2mm_clearance</t>
-  </si>
-  <si>
     <t>USB4151-GF-C</t>
   </si>
   <si>
@@ -90,15 +81,6 @@
     <t>robot:GCT_USB4151-GF-C_REVA</t>
   </si>
   <si>
-    <t>Conn_01x16</t>
-  </si>
-  <si>
-    <t>J9</t>
-  </si>
-  <si>
-    <t>robot:Castellated 1x16 2.54mm</t>
-  </si>
-  <si>
     <t>0.47uH</t>
   </si>
   <si>
@@ -109,18 +91,6 @@
   </si>
   <si>
     <t>IHLP2020BZERR47M01</t>
-  </si>
-  <si>
-    <t>NetTie_2</t>
-  </si>
-  <si>
-    <t>NT21,NT22</t>
-  </si>
-  <si>
-    <t>robot:NetTie-_SMD_Pad6mil</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>100k</t>
@@ -911,22 +881,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>248961</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>57610</xdr:rowOff>
+      <xdr:colOff>753790</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>86265</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2E108C5-3FBB-4E9B-80D0-6AA0D16B4BF6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70C6E302-217D-42C6-9936-DDADD58D8561}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -942,8 +912,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6248400" y="962025"/>
-          <a:ext cx="9392961" cy="3296110"/>
+          <a:off x="6724650" y="228600"/>
+          <a:ext cx="9421540" cy="3867690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>182311</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>104965</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{463B72EA-CC9F-4935-9F95-5F43125788E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6762750" y="4276725"/>
+          <a:ext cx="9573961" cy="1362265"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1252,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1263,10 +1277,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1339,7 +1353,10 @@
       <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
@@ -1352,146 +1369,147 @@
         <v>20</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="5"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="6">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="6">
-        <v>10</v>
+      <c r="A13" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="6" t="s">
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="6">
+        <v>0</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="6" t="s">
+      <c r="C15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6">
+        <v>0</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1499,46 +1517,46 @@
         <v>0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="D19" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="B20" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6">
-        <v>0</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="6" t="s">
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6">
-        <v>0</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>61</v>
@@ -1547,7 +1565,7 @@
         <v>62</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1561,22 +1579,23 @@
         <v>65</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>69</v>
-      </c>
+      <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
@@ -1591,63 +1610,20 @@
       <c r="D24" s="6" t="s">
         <v>70</v>
       </c>
+      <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="3" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/pcb/robot/usb-pd-module/USB_PD_Module_BOM.xlsx
+++ b/pcb/robot/usb-pd-module/USB_PD_Module_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JHORDAN\FREELANCE\PROYECTOS\KICAD_USB_PD_MODULAR\Github\smartphone-robot-cad\pcb\robot\usb-pd-module\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA19E2AD-F65F-4F97-B000-E668666198BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8FC6BD-3A8F-47F7-867B-8DFDD6C4D706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="84">
   <si>
     <t>Footprint</t>
   </si>
@@ -306,6 +306,12 @@
   </si>
   <si>
     <t>RC0603JR-07120KL</t>
+  </si>
+  <si>
+    <t>RC0402FR-07100RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-07422RL</t>
   </si>
 </sst>
 </file>
@@ -850,7 +856,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -861,7 +867,9 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -926,22 +934,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>81644</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>553910</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>10111</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>610921</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>159724</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8341EDA9-660D-4292-BA42-7D0C2C5726FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36443C27-EBEC-4777-AC76-3C9D1328A0AE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -957,8 +965,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7772400" y="1362075"/>
-          <a:ext cx="10459910" cy="4201111"/>
+          <a:off x="8749393" y="1251858"/>
+          <a:ext cx="9469171" cy="3724795"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1272,8 +1280,10 @@
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
     <col min="4" max="4" width="27.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75">
@@ -1289,6 +1299,8 @@
       <c r="D1" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
@@ -1303,8 +1315,8 @@
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
@@ -1319,8 +1331,8 @@
       <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
@@ -1335,8 +1347,8 @@
       <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
@@ -1351,8 +1363,8 @@
       <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="16.5">
       <c r="A6" s="5" t="s">
@@ -1367,10 +1379,10 @@
       <c r="D6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="8">
         <v>2188470001</v>
       </c>
     </row>
@@ -1387,10 +1399,10 @@
       <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" ht="16.5">
       <c r="A8" s="3">
         <v>100</v>
       </c>
@@ -1400,11 +1412,13 @@
       <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="D8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" ht="16.5">
       <c r="A9" s="3">
         <v>422</v>
       </c>
@@ -1414,9 +1428,11 @@
       <c r="C9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="D9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
@@ -1431,8 +1447,8 @@
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5">
@@ -1447,10 +1463,10 @@
       <c r="D11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="5" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1467,8 +1483,8 @@
       <c r="D12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
@@ -1483,10 +1499,10 @@
       <c r="D13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="5" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1503,10 +1519,10 @@
       <c r="D14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="5" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1523,10 +1539,10 @@
       <c r="D15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1543,8 +1559,8 @@
       <c r="D16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3">
@@ -1559,8 +1575,8 @@
       <c r="D17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3">
@@ -1575,8 +1591,8 @@
       <c r="D18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
@@ -1591,8 +1607,8 @@
       <c r="D19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
@@ -1604,11 +1620,11 @@
       <c r="C20" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
@@ -1623,8 +1639,8 @@
       <c r="D21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
@@ -1639,8 +1655,8 @@
       <c r="D22" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
@@ -1655,8 +1671,8 @@
       <c r="D23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
@@ -1671,8 +1687,8 @@
       <c r="D24" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
@@ -1687,8 +1703,8 @@
       <c r="D25" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="4"/>

--- a/pcb/robot/usb-pd-module/USB_PD_Module_BOM.xlsx
+++ b/pcb/robot/usb-pd-module/USB_PD_Module_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JHORDAN\FREELANCE\PROYECTOS\KICAD_USB_PD_MODULAR\Github\smartphone-robot-cad\pcb\robot\usb-pd-module\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061915B7-0919-4C28-9B35-08341C0054FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985A3A1D-592C-47D0-B16D-9C6519FB0B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
   <si>
     <t>Footprint</t>
   </si>
@@ -262,13 +262,16 @@
   </si>
   <si>
     <t>Designator</t>
+  </si>
+  <si>
+    <t>7-10 Workdays</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,8 +425,13 @@
       <name val="Arial"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -601,12 +609,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -748,13 +750,17 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -805,7 +811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -814,9 +820,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -882,8 +891,8 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
@@ -904,16 +913,15 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect t="66001"/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6724650" y="228600"/>
-          <a:ext cx="9421540" cy="3867690"/>
+          <a:off x="6724650" y="2781300"/>
+          <a:ext cx="9421540" cy="1314990"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -925,22 +933,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>182311</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>410853</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>104965</xdr:rowOff>
+      <xdr:rowOff>162099</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 3">
+        <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{463B72EA-CC9F-4935-9F95-5F43125788E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06C95DCE-9967-4A4B-B6A1-BDCD2E4C79CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -956,8 +964,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6762750" y="4276725"/>
-          <a:ext cx="9573961" cy="1362265"/>
+          <a:off x="6648450" y="4067175"/>
+          <a:ext cx="9154803" cy="1247949"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>639481</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>133712</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0879C32-4CD3-4829-9822-B7EA59AEFAFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6677025" y="28575"/>
+          <a:ext cx="9354856" cy="2591162"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1286,6 +1338,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="2"/>
+      <c r="E1" s="5"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
@@ -1300,6 +1353,7 @@
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
@@ -1314,6 +1368,7 @@
       <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
@@ -1328,289 +1383,311 @@
       <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>10</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>36</v>
       </c>
+      <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>0</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>47</v>
       </c>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>0</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>50</v>
       </c>
+      <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>0</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>53</v>
       </c>
+      <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>59</v>
       </c>
+      <c r="E20" s="7" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>60</v>
       </c>
+      <c r="E21" s="7" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="4" t="s">
         <v>66</v>
       </c>
+      <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="6"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
@@ -1625,6 +1702,7 @@
       <c r="D25" s="3" t="s">
         <v>76</v>
       </c>
+      <c r="E25" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
